--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N447"/>
+  <dimension ref="A1:N448"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13334,6 +13334,52 @@
         <v>0.1490024287395885</v>
       </c>
     </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>2026-09-06 00:00:00</t>
+        </is>
+      </c>
+      <c r="B448" t="n">
+        <v>152000</v>
+      </c>
+      <c r="C448" t="n">
+        <v>22564.99</v>
+      </c>
+      <c r="D448" t="n">
+        <v>19969.01</v>
+      </c>
+      <c r="E448" t="n">
+        <v>109975</v>
+      </c>
+      <c r="F448" t="n">
+        <v>16326.21</v>
+      </c>
+      <c r="G448" t="n">
+        <v>14447.98</v>
+      </c>
+      <c r="H448" t="n">
+        <v>24360</v>
+      </c>
+      <c r="I448" t="n">
+        <v>3616.34</v>
+      </c>
+      <c r="J448" t="n">
+        <v>3200.3</v>
+      </c>
+      <c r="K448" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L448" t="n">
+        <v>17814.46</v>
+      </c>
+      <c r="M448" t="n">
+        <v>15765.01</v>
+      </c>
+      <c r="N448" t="n">
+        <v>0.1490024287395885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N448"/>
+  <dimension ref="A1:N449"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13380,6 +13380,52 @@
         <v>0.1490024287395885</v>
       </c>
     </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>2026-09-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="B449" t="n">
+        <v>147500</v>
+      </c>
+      <c r="C449" t="n">
+        <v>21922.33</v>
+      </c>
+      <c r="D449" t="n">
+        <v>19400.29</v>
+      </c>
+      <c r="E449" t="n">
+        <v>109905</v>
+      </c>
+      <c r="F449" t="n">
+        <v>16334.74</v>
+      </c>
+      <c r="G449" t="n">
+        <v>14455.52</v>
+      </c>
+      <c r="H449" t="n">
+        <v>24410</v>
+      </c>
+      <c r="I449" t="n">
+        <v>3627.96</v>
+      </c>
+      <c r="J449" t="n">
+        <v>3210.58</v>
+      </c>
+      <c r="K449" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L449" t="n">
+        <v>17835.11</v>
+      </c>
+      <c r="M449" t="n">
+        <v>15783.29</v>
+      </c>
+      <c r="N449" t="n">
+        <v>0.1490024287395885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N449"/>
+  <dimension ref="A1:N450"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13426,6 +13426,52 @@
         <v>0.1490024287395885</v>
       </c>
     </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>2026-09-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="B450" t="n">
+        <v>146750</v>
+      </c>
+      <c r="C450" t="n">
+        <v>21814.1</v>
+      </c>
+      <c r="D450" t="n">
+        <v>19304.51</v>
+      </c>
+      <c r="E450" t="n">
+        <v>111255</v>
+      </c>
+      <c r="F450" t="n">
+        <v>16537.84</v>
+      </c>
+      <c r="G450" t="n">
+        <v>14635.25</v>
+      </c>
+      <c r="H450" t="n">
+        <v>24460</v>
+      </c>
+      <c r="I450" t="n">
+        <v>3635.93</v>
+      </c>
+      <c r="J450" t="n">
+        <v>3217.64</v>
+      </c>
+      <c r="K450" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L450" t="n">
+        <v>17837.77</v>
+      </c>
+      <c r="M450" t="n">
+        <v>15785.63</v>
+      </c>
+      <c r="N450" t="n">
+        <v>0.1490024287395885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N450"/>
+  <dimension ref="A1:N451"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13472,6 +13472,50 @@
         <v>0.1490024287395885</v>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>2026-09-22 00:00:00</t>
+        </is>
+      </c>
+      <c r="B451" t="n">
+        <v>134450</v>
+      </c>
+      <c r="C451" t="n">
+        <v>20032.48</v>
+      </c>
+      <c r="D451" t="n">
+        <v>17727.86</v>
+      </c>
+      <c r="E451" t="n">
+        <v>112735</v>
+      </c>
+      <c r="F451" t="n">
+        <v>16797.04</v>
+      </c>
+      <c r="G451" t="n">
+        <v>14864.64</v>
+      </c>
+      <c r="H451" t="n">
+        <v>24270</v>
+      </c>
+      <c r="I451" t="n">
+        <v>3616.13</v>
+      </c>
+      <c r="J451" t="n">
+        <v>3200.11</v>
+      </c>
+      <c r="K451" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L451" t="n">
+        <v>17879.49</v>
+      </c>
+      <c r="M451" t="n">
+        <v>15822.56</v>
+      </c>
+      <c r="N451" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N451"/>
+  <dimension ref="A1:N452"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13516,6 +13516,50 @@
       </c>
       <c r="N451" t="inlineStr"/>
     </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>2026-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="B452" t="n">
+        <v>135200</v>
+      </c>
+      <c r="C452" t="n">
+        <v>20130.43</v>
+      </c>
+      <c r="D452" t="n">
+        <v>17814.54</v>
+      </c>
+      <c r="E452" t="n">
+        <v>112495</v>
+      </c>
+      <c r="F452" t="n">
+        <v>16749.8</v>
+      </c>
+      <c r="G452" t="n">
+        <v>14822.83</v>
+      </c>
+      <c r="H452" t="n">
+        <v>24240</v>
+      </c>
+      <c r="I452" t="n">
+        <v>3609.18</v>
+      </c>
+      <c r="J452" t="n">
+        <v>3193.97</v>
+      </c>
+      <c r="K452" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L452" t="n">
+        <v>18165.03</v>
+      </c>
+      <c r="M452" t="n">
+        <v>16075.25</v>
+      </c>
+      <c r="N452" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N452"/>
+  <dimension ref="A1:N453"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13560,6 +13560,50 @@
       </c>
       <c r="N452" t="inlineStr"/>
     </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>2026-09-24 00:00:00</t>
+        </is>
+      </c>
+      <c r="B453" t="n">
+        <v>133150</v>
+      </c>
+      <c r="C453" t="n">
+        <v>19786.6</v>
+      </c>
+      <c r="D453" t="n">
+        <v>17510.27</v>
+      </c>
+      <c r="E453" t="n">
+        <v>112085</v>
+      </c>
+      <c r="F453" t="n">
+        <v>16656.26</v>
+      </c>
+      <c r="G453" t="n">
+        <v>14740.06</v>
+      </c>
+      <c r="H453" t="n">
+        <v>24240</v>
+      </c>
+      <c r="I453" t="n">
+        <v>3602.16</v>
+      </c>
+      <c r="J453" t="n">
+        <v>3187.75</v>
+      </c>
+      <c r="K453" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L453" t="n">
+        <v>18129.67</v>
+      </c>
+      <c r="M453" t="n">
+        <v>16043.96</v>
+      </c>
+      <c r="N453" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N453"/>
+  <dimension ref="A1:N454"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13604,6 +13604,50 @@
       </c>
       <c r="N453" t="inlineStr"/>
     </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>2026-09-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="B454" t="n">
+        <v>133150</v>
+      </c>
+      <c r="C454" t="n">
+        <v>19786.6</v>
+      </c>
+      <c r="D454" t="n">
+        <v>17510.27</v>
+      </c>
+      <c r="E454" t="n">
+        <v>112085</v>
+      </c>
+      <c r="F454" t="n">
+        <v>16656.26</v>
+      </c>
+      <c r="G454" t="n">
+        <v>14740.06</v>
+      </c>
+      <c r="H454" t="n">
+        <v>24240</v>
+      </c>
+      <c r="I454" t="n">
+        <v>3602.16</v>
+      </c>
+      <c r="J454" t="n">
+        <v>3187.75</v>
+      </c>
+      <c r="K454" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L454" t="n">
+        <v>18129.67</v>
+      </c>
+      <c r="M454" t="n">
+        <v>16043.96</v>
+      </c>
+      <c r="N454" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N454"/>
+  <dimension ref="A1:N455"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13648,6 +13648,50 @@
       </c>
       <c r="N454" t="inlineStr"/>
     </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>2026-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="B455" t="n">
+        <v>133150</v>
+      </c>
+      <c r="C455" t="n">
+        <v>19786.6</v>
+      </c>
+      <c r="D455" t="n">
+        <v>17510.27</v>
+      </c>
+      <c r="E455" t="n">
+        <v>112085</v>
+      </c>
+      <c r="F455" t="n">
+        <v>16656.26</v>
+      </c>
+      <c r="G455" t="n">
+        <v>14740.06</v>
+      </c>
+      <c r="H455" t="n">
+        <v>24240</v>
+      </c>
+      <c r="I455" t="n">
+        <v>3602.16</v>
+      </c>
+      <c r="J455" t="n">
+        <v>3187.75</v>
+      </c>
+      <c r="K455" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L455" t="n">
+        <v>18129.67</v>
+      </c>
+      <c r="M455" t="n">
+        <v>16043.96</v>
+      </c>
+      <c r="N455" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N455"/>
+  <dimension ref="A1:N456"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13692,6 +13692,50 @@
       </c>
       <c r="N455" t="inlineStr"/>
     </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>2026-09-27 00:00:00</t>
+        </is>
+      </c>
+      <c r="B456" t="n">
+        <v>133150</v>
+      </c>
+      <c r="C456" t="n">
+        <v>19786.6</v>
+      </c>
+      <c r="D456" t="n">
+        <v>17510.27</v>
+      </c>
+      <c r="E456" t="n">
+        <v>112085</v>
+      </c>
+      <c r="F456" t="n">
+        <v>16656.26</v>
+      </c>
+      <c r="G456" t="n">
+        <v>14740.06</v>
+      </c>
+      <c r="H456" t="n">
+        <v>24240</v>
+      </c>
+      <c r="I456" t="n">
+        <v>3602.16</v>
+      </c>
+      <c r="J456" t="n">
+        <v>3187.75</v>
+      </c>
+      <c r="K456" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L456" t="n">
+        <v>18129.67</v>
+      </c>
+      <c r="M456" t="n">
+        <v>16043.96</v>
+      </c>
+      <c r="N456" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N456"/>
+  <dimension ref="A1:N457"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13736,6 +13736,50 @@
       </c>
       <c r="N456" t="inlineStr"/>
     </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>2026-09-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="B457" t="n">
+        <v>126350</v>
+      </c>
+      <c r="C457" t="n">
+        <v>18768.01</v>
+      </c>
+      <c r="D457" t="n">
+        <v>16608.86</v>
+      </c>
+      <c r="E457" t="n">
+        <v>111175</v>
+      </c>
+      <c r="F457" t="n">
+        <v>16513.92</v>
+      </c>
+      <c r="G457" t="n">
+        <v>14614.09</v>
+      </c>
+      <c r="H457" t="n">
+        <v>24170</v>
+      </c>
+      <c r="I457" t="n">
+        <v>3590.21</v>
+      </c>
+      <c r="J457" t="n">
+        <v>3177.18</v>
+      </c>
+      <c r="K457" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L457" t="n">
+        <v>18121.86</v>
+      </c>
+      <c r="M457" t="n">
+        <v>16037.05</v>
+      </c>
+      <c r="N457" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N457"/>
+  <dimension ref="A1:N458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13780,6 +13780,50 @@
       </c>
       <c r="N457" t="inlineStr"/>
     </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>2026-09-29 00:00:00</t>
+        </is>
+      </c>
+      <c r="B458" t="n">
+        <v>123400</v>
+      </c>
+      <c r="C458" t="n">
+        <v>18342.62</v>
+      </c>
+      <c r="D458" t="n">
+        <v>16232.41</v>
+      </c>
+      <c r="E458" t="n">
+        <v>110990</v>
+      </c>
+      <c r="F458" t="n">
+        <v>16497.96</v>
+      </c>
+      <c r="G458" t="n">
+        <v>14599.96</v>
+      </c>
+      <c r="H458" t="n">
+        <v>24110</v>
+      </c>
+      <c r="I458" t="n">
+        <v>3583.8</v>
+      </c>
+      <c r="J458" t="n">
+        <v>3171.5</v>
+      </c>
+      <c r="K458" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L458" t="n">
+        <v>18134.52</v>
+      </c>
+      <c r="M458" t="n">
+        <v>16048.25</v>
+      </c>
+      <c r="N458" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N458"/>
+  <dimension ref="A1:N459"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13824,6 +13824,50 @@
       </c>
       <c r="N458" t="inlineStr"/>
     </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>2026-09-30 00:00:00</t>
+        </is>
+      </c>
+      <c r="B459" t="n">
+        <v>122800</v>
+      </c>
+      <c r="C459" t="n">
+        <v>18258.32</v>
+      </c>
+      <c r="D459" t="n">
+        <v>16157.81</v>
+      </c>
+      <c r="E459" t="n">
+        <v>111360</v>
+      </c>
+      <c r="F459" t="n">
+        <v>16557.38</v>
+      </c>
+      <c r="G459" t="n">
+        <v>14652.55</v>
+      </c>
+      <c r="H459" t="n">
+        <v>24030</v>
+      </c>
+      <c r="I459" t="n">
+        <v>3572.86</v>
+      </c>
+      <c r="J459" t="n">
+        <v>3161.83</v>
+      </c>
+      <c r="K459" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L459" t="n">
+        <v>18139.38</v>
+      </c>
+      <c r="M459" t="n">
+        <v>16052.54</v>
+      </c>
+      <c r="N459" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N459"/>
+  <dimension ref="A1:N460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13868,6 +13868,50 @@
       </c>
       <c r="N459" t="inlineStr"/>
     </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>2026-10-01 00:00:00</t>
+        </is>
+      </c>
+      <c r="B460" t="n">
+        <v>122800</v>
+      </c>
+      <c r="C460" t="n">
+        <v>18258.32</v>
+      </c>
+      <c r="D460" t="n">
+        <v>16157.81</v>
+      </c>
+      <c r="E460" t="n">
+        <v>111360</v>
+      </c>
+      <c r="F460" t="n">
+        <v>16557.38</v>
+      </c>
+      <c r="G460" t="n">
+        <v>14652.55</v>
+      </c>
+      <c r="H460" t="n">
+        <v>24030</v>
+      </c>
+      <c r="I460" t="n">
+        <v>3572.86</v>
+      </c>
+      <c r="J460" t="n">
+        <v>3161.83</v>
+      </c>
+      <c r="K460" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L460" t="n">
+        <v>18139.38</v>
+      </c>
+      <c r="M460" t="n">
+        <v>16052.54</v>
+      </c>
+      <c r="N460" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N460"/>
+  <dimension ref="A1:N461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13912,6 +13912,50 @@
       </c>
       <c r="N460" t="inlineStr"/>
     </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>2026-10-08 00:00:00</t>
+        </is>
+      </c>
+      <c r="B461" t="n">
+        <v>124950</v>
+      </c>
+      <c r="C461" t="n">
+        <v>18577.44</v>
+      </c>
+      <c r="D461" t="n">
+        <v>16440.21</v>
+      </c>
+      <c r="E461" t="n">
+        <v>112545</v>
+      </c>
+      <c r="F461" t="n">
+        <v>16733.08</v>
+      </c>
+      <c r="G461" t="n">
+        <v>14808.03</v>
+      </c>
+      <c r="H461" t="n">
+        <v>23760</v>
+      </c>
+      <c r="I461" t="n">
+        <v>3532.61</v>
+      </c>
+      <c r="J461" t="n">
+        <v>3126.21</v>
+      </c>
+      <c r="K461" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L461" t="n">
+        <v>18138.84</v>
+      </c>
+      <c r="M461" t="n">
+        <v>16052.07</v>
+      </c>
+      <c r="N461" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N461"/>
+  <dimension ref="A1:N462"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13956,6 +13956,50 @@
       </c>
       <c r="N461" t="inlineStr"/>
     </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>2026-10-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="B462" t="n">
+        <v>122350</v>
+      </c>
+      <c r="C462" t="n">
+        <v>18201.43</v>
+      </c>
+      <c r="D462" t="n">
+        <v>16107.46</v>
+      </c>
+      <c r="E462" t="n">
+        <v>111465</v>
+      </c>
+      <c r="F462" t="n">
+        <v>16582.12</v>
+      </c>
+      <c r="G462" t="n">
+        <v>14674.44</v>
+      </c>
+      <c r="H462" t="n">
+        <v>23650</v>
+      </c>
+      <c r="I462" t="n">
+        <v>3518.3</v>
+      </c>
+      <c r="J462" t="n">
+        <v>3113.54</v>
+      </c>
+      <c r="K462" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L462" t="n">
+        <v>18149.36</v>
+      </c>
+      <c r="M462" t="n">
+        <v>16061.38</v>
+      </c>
+      <c r="N462" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N462"/>
+  <dimension ref="A1:N463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14000,6 +14000,50 @@
       </c>
       <c r="N462" t="inlineStr"/>
     </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>2026-10-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="B463" t="n">
+        <v>122350</v>
+      </c>
+      <c r="C463" t="n">
+        <v>18201.43</v>
+      </c>
+      <c r="D463" t="n">
+        <v>16107.46</v>
+      </c>
+      <c r="E463" t="n">
+        <v>111465</v>
+      </c>
+      <c r="F463" t="n">
+        <v>16582.12</v>
+      </c>
+      <c r="G463" t="n">
+        <v>14674.44</v>
+      </c>
+      <c r="H463" t="n">
+        <v>23650</v>
+      </c>
+      <c r="I463" t="n">
+        <v>3518.3</v>
+      </c>
+      <c r="J463" t="n">
+        <v>3113.54</v>
+      </c>
+      <c r="K463" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L463" t="n">
+        <v>18149.36</v>
+      </c>
+      <c r="M463" t="n">
+        <v>16061.38</v>
+      </c>
+      <c r="N463" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N463"/>
+  <dimension ref="A1:N464"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14044,6 +14044,50 @@
       </c>
       <c r="N463" t="inlineStr"/>
     </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>2026-10-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="B464" t="n">
+        <v>122350</v>
+      </c>
+      <c r="C464" t="n">
+        <v>18201.43</v>
+      </c>
+      <c r="D464" t="n">
+        <v>16107.46</v>
+      </c>
+      <c r="E464" t="n">
+        <v>111465</v>
+      </c>
+      <c r="F464" t="n">
+        <v>16582.12</v>
+      </c>
+      <c r="G464" t="n">
+        <v>14674.44</v>
+      </c>
+      <c r="H464" t="n">
+        <v>23650</v>
+      </c>
+      <c r="I464" t="n">
+        <v>3518.3</v>
+      </c>
+      <c r="J464" t="n">
+        <v>3113.54</v>
+      </c>
+      <c r="K464" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L464" t="n">
+        <v>18149.36</v>
+      </c>
+      <c r="M464" t="n">
+        <v>16061.38</v>
+      </c>
+      <c r="N464" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N464"/>
+  <dimension ref="A1:N465"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14088,6 +14088,50 @@
       </c>
       <c r="N464" t="inlineStr"/>
     </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>2026-10-12 00:00:00</t>
+        </is>
+      </c>
+      <c r="B465" t="n">
+        <v>115400</v>
+      </c>
+      <c r="C465" t="n">
+        <v>17197.96</v>
+      </c>
+      <c r="D465" t="n">
+        <v>15219.43</v>
+      </c>
+      <c r="E465" t="n">
+        <v>111915</v>
+      </c>
+      <c r="F465" t="n">
+        <v>16678.59</v>
+      </c>
+      <c r="G465" t="n">
+        <v>14759.81</v>
+      </c>
+      <c r="H465" t="n">
+        <v>23810</v>
+      </c>
+      <c r="I465" t="n">
+        <v>3548.38</v>
+      </c>
+      <c r="J465" t="n">
+        <v>3140.16</v>
+      </c>
+      <c r="K465" t="n">
+        <v>122000</v>
+      </c>
+      <c r="L465" t="n">
+        <v>18181.55</v>
+      </c>
+      <c r="M465" t="n">
+        <v>16089.86</v>
+      </c>
+      <c r="N465" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Price Data.xlsx
+++ b/Price Data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N465"/>
+  <dimension ref="A1:N466"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14132,6 +14132,50 @@
       </c>
       <c r="N465" t="inlineStr"/>
     </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>2026-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="B466" t="n">
+        <v>111650</v>
+      </c>
+      <c r="C466" t="n">
+        <v>16638.85</v>
+      </c>
+      <c r="D466" t="n">
+        <v>14724.64</v>
+      </c>
+      <c r="E466" t="n">
+        <v>111390</v>
+      </c>
+      <c r="F466" t="n">
+        <v>16600.1</v>
+      </c>
+      <c r="G466" t="n">
+        <v>14690.35</v>
+      </c>
+      <c r="H466" t="n">
+        <v>23710</v>
+      </c>
+      <c r="I466" t="n">
+        <v>3533.43</v>
+      </c>
+      <c r="J466" t="n">
+        <v>3126.93</v>
+      </c>
+      <c r="K466" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L466" t="n">
+        <v>17883.22</v>
+      </c>
+      <c r="M466" t="n">
+        <v>15825.86</v>
+      </c>
+      <c r="N466" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
